--- a/data/trans_bre/P1804_2016_2023-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P1804_2016_2023-Provincia-trans_bre.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2,1</t>
+          <t>3,32</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>138,23%</t>
+          <t>253,78%</t>
         </is>
       </c>
     </row>
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,69; 12,26</t>
+          <t>1,48; 12,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 4,25</t>
+          <t>1,3; 5,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,93; 243,42</t>
+          <t>12,87; 233,58</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-12,39; 702,79</t>
+          <t>24,42; 860,53</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1,42</t>
+          <t>1,58</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>373,29%</t>
+          <t>439,29%</t>
         </is>
       </c>
     </row>
@@ -661,17 +661,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 4,98</t>
+          <t>-1,3; 4,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,23; 3,21</t>
+          <t>0,27; 3,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-17,56; 153,31</t>
+          <t>-22,17; 139,82</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4,11</t>
+          <t>4,25</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>110,33%</t>
+          <t>116,83%</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 4,82</t>
+          <t>-0,49; 5,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,07; 7,53</t>
+          <t>1,24; 7,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-25,99; 409,27</t>
+          <t>-29,06; 405,22</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14,64; 294,68</t>
+          <t>18,66; 318,17</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-7,8</t>
+          <t>-0,28</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-22,95%</t>
+          <t>-0,82%</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,96; 14,62</t>
+          <t>1,57; 13,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-19,4; 1,7</t>
+          <t>-7,73; 7,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,65; 79,81</t>
+          <t>6,29; 78,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-52,02; 4,4</t>
+          <t>-19,84; 26,85</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>63,33%</t>
+          <t>66,59%</t>
         </is>
       </c>
     </row>
@@ -841,22 +841,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 5,82</t>
+          <t>-2,04; 5,94</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 2,21</t>
+          <t>-1,12; 2,29</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-46,55; 387,57</t>
+          <t>-49,15; 405,92</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-67,76; 626,37</t>
+          <t>-65,6; 801,92</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2,64</t>
+          <t>3,4</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>41,95%</t>
+          <t>55,9%</t>
         </is>
       </c>
     </row>
@@ -901,12 +901,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,04; 5,26</t>
+          <t>1,24; 5,52</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 6,36</t>
+          <t>-0,49; 7,48</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-17,03; 138,15</t>
+          <t>-8,76; 167,31</t>
         </is>
       </c>
     </row>
@@ -938,7 +938,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1,5</t>
+          <t>3,56</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>63,23%</t>
         </is>
       </c>
     </row>
@@ -961,22 +961,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 4,96</t>
+          <t>-0,34; 4,92</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 4,96</t>
+          <t>0,67; 6,38</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,73; 144,67</t>
+          <t>-6,24; 141,93</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-45,91; 104,37</t>
+          <t>8,65; 148,45</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1,25</t>
+          <t>0,87</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>49,83%</t>
         </is>
       </c>
     </row>
@@ -1021,22 +1021,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,29; 6,9</t>
+          <t>1,39; 6,93</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 2,9</t>
+          <t>-0,46; 2,18</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16,07; 145,97</t>
+          <t>18,88; 153,68</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-8,45; 396,42</t>
+          <t>-21,42; 212,05</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2,05</t>
+          <t>2,34</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>37,81%</t>
         </is>
       </c>
     </row>
@@ -1081,22 +1081,22 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,38; 4,98</t>
+          <t>2,17; 4,92</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,58; 3,76</t>
+          <t>1,07; 3,51</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>33,36; 87,3</t>
+          <t>31,87; 88,4</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9,0; 81,83</t>
+          <t>15,88; 64,21</t>
         </is>
       </c>
     </row>
